--- a/consolidation/output/final_prd_scopped.xlsx
+++ b/consolidation/output/final_prd_scopped.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N2"/>
+  <dimension ref="A1:N10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -562,6 +562,538 @@
       <c r="N2" t="inlineStr">
         <is>
           <t>Having too many product names for the same reference is inefficient and can induce user errors during the OOBE process.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>R&amp;D</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Performance/Feature</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Supplies Reliability</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>NGB Keyed Bottles with High Yield: Develop new NGB keyed bottles supporting 6,000-page yield for black and CMY, with CMY bottle size &gt;8,000 pages.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Increases ink capacity and reduces customer intervention, aligning with competitive CISS offerings.</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Bottles must deliver 6,000-page yield for black and CMY, with CMY bottle size &gt;8,000 pages in standard ISO tests; must be keyed to prevent incorrect insertion.</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Bottles deliver 6,000-page yield for black and CMY, with CMY bottle size &gt;8,000 pages in standard ISO tests; must be keyed to prevent incorrect insertion.</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>Increases ink capacity and reduces customer intervention, aligning with competitive CISS offerings.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>R&amp;D</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Quality Improvement &amp; Serviceability</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Supplies Reliability</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Spill-Free Reliability for Ink Bottles: Ensure the new NGB bottles provide spill-free operation during installation and use.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Enhances user experience and reduces service costs related to ink spills.</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>No ink spill observed in 100% of installation tests under normal conditions.</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>No ink spill observed in 100% of installation tests under normal conditions.</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>Enhances user experience and reduces service costs related to ink spills.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>R&amp;D</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Quality Improvement &amp; Serviceability</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>HW Spec</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>NOA-F with Metal Foiled Labyrinth and Lid Label: Integrate NOA-F component with a metal foiled labyrinth and lid label for improved performance.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Improves reliability and traceability of the NOA-F component.</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>All NOA-F units include metal foiled labyrinth and lid label as verified in quality audits.</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>All NOA-F units include metal foiled labyrinth and lid label.</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>Improves reliability and traceability of the NOA-F component.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>4</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Supportability &amp; Serviciablity</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Serviceability</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Support for Customer Replaceable PHA and NOA-F: Enable end customers to replace PHA and NOA-F components themselves.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Reduces service costs and downtime for customers, improving satisfaction.</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Customers can replace PHA and NOA-F without tools within 5 minutes following provided instructions.</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Customers can replace PHA and NOA-F without tools within 5 minutes.</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>Reduces service costs and downtime for customers, improving satisfaction.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>R&amp;D</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Performance/Feature</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>HW Spec</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Reddington ID</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Product ID with Increased Tank Size: Increase the tank size for the Reddington ID product variant, ensuring no change to Marconi-HI ADF.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Supports higher ink capacity and longer use between refills.</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Tank size increased as per specifications; no interference with ADF operation.</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Tank size increased as per specifications; no interference with ADF operation.</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>Supports higher ink capacity and longer use between refills.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>8</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>R&amp;D</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Performance/Feature</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>HW Spec</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Input and Output Tray Redesign for Tank Protrusion: Modify input and output trays to accommodate the increased tank protrusion due to larger ink tanks.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Ensures mechanical compatibility and user convenience.</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Trays function correctly with new tank dimensions; verified in assembly and user testing.</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Trays function correctly with new tank dimensions.</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>Ensures mechanical compatibility and user convenience.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>9</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Design/UI</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Control Panel</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>4.3” CGD Display Integration: Integrate a 4.3” CGD display into the product for improved user interface.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Enhances usability and aligns with modern user expectations.</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Display operates with full functionality; passes usability and reliability tests.</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Display operates with full functionality.</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>Enhances usability and aligns with modern user expectations.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>10</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>R&amp;D</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Quality Improvement &amp; Serviceability</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Print Quality</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Service Station Aerosol Management with Spit Platform Changes: Implement aerosol management in the service station to handle changes due to increased tank size and spit platform updates.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Maintains print quality and prevents contamination inside the printer.</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>No aerosol-related print defects or contamination after 80,000 pages of operation.</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>No aerosol-related print defects or contamination after 80,000 pages of operation.</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>Maintains print quality and prevents contamination inside the printer.</t>
         </is>
       </c>
     </row>
@@ -589,7 +1121,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N5"/>
+  <dimension ref="A1:N7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -941,6 +1473,142 @@
       <c r="N5" t="inlineStr">
         <is>
           <t>To check if there is a Print Quality issue when the printer is operated while on a trolley.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Reliability</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Durability</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Warranty Page Life Goal of 80,000 Pages: Set and support a new warranty page life goal of 80,000 pages for the printer.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Enhances product value and aligns with new competitive benchmarks.</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Device must operate without major failure for 80,000 pages under standard usage conditions.</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Device operates without major failure for 80,000 pages under standard usage conditions.</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>extended supporting document</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>Enhances product value and aligns with new competitive benchmarks.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>7</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Tech Reg</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Environmental &amp; Sustainability</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Environmental Ecolabel</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>PDL SKU</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>EPEAT3, LOT4, and Blue Angel Compliance for PDL SKU: Ensure the PDL SKU meets EPEAT3, LOT4, and Blue Angel environmental requirements.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Mandatory for market access and sustainability goals.</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Product passes all required certifications prior to launch.</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Product passes all required certifications prior to launch.</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>extended supporting document</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>Mandatory for market access and sustainability goals.</t>
         </is>
       </c>
     </row>

--- a/consolidation/output/final_prd_scopped.xlsx
+++ b/consolidation/output/final_prd_scopped.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N2"/>
+  <dimension ref="A1:N10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -566,6 +566,538 @@
 HP OJP 9010e All-in-One Printer series
 HP OJP 9010 All-in-One Printer
 Have too many names isn't efficient and can induce user errors</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>R&amp;D</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Performance/Feature</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Supplies Reliability</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>NGB Keyed Bottles with High Yield: Develop new NGB keyed bottles supporting 6,000-page yield for black and CMY, with CMY bottle size &gt;8,000 pages.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Increases ink capacity and reduces customer intervention, aligning with competitive CISS offerings.</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Bottles must deliver 6,000-page yield for black and CMY, with CMY bottle size &gt;8,000 pages in standard ISO tests; must be keyed to prevent incorrect insertion.</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Bottles deliver 6,000-page yield for black and CMY, with CMY bottle size &gt;8,000 pages in standard ISO tests; must be keyed to prevent incorrect insertion.</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>Increases ink capacity and reduces customer intervention, aligning with competitive CISS offerings.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>R&amp;D</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Quality Improvement &amp; Serviceability</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Supplies Reliability</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Spill-Free Reliability for Ink Bottles: Ensure the new NGB bottles provide spill-free operation during installation and use.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Enhances user experience and reduces service costs related to ink spills.</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>No ink spill observed in 100% of installation tests under normal conditions.</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>No ink spill observed in 100% of installation tests under normal conditions.</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>Enhances user experience and reduces service costs related to ink spills.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>R&amp;D</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Quality Improvement &amp; Serviceability</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>HW Spec</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>NOA-F with Metal Foiled Labyrinth and Lid Label: Integrate NOA-F component with a metal foiled labyrinth and lid label for improved performance.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Improves reliability and traceability of the NOA-F component.</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>All NOA-F units include metal foiled labyrinth and lid label as verified in quality audits.</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>All NOA-F units include metal foiled labyrinth and lid label.</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>Improves reliability and traceability of the NOA-F component.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>4</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Supportability &amp; Serviciablity</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Serviceability</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Support for Customer Replaceable PHA and NOA-F: Enable end customers to replace PHA and NOA-F components themselves.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Reduces service costs and downtime for customers, improving satisfaction.</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Customers can replace PHA and NOA-F without tools within 5 minutes following provided instructions.</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Customers can replace PHA and NOA-F without tools within 5 minutes.</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>Reduces service costs and downtime for customers, improving satisfaction.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>R&amp;D</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Performance/Feature</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>HW Spec</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Reddington ID</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Product ID with Increased Tank Size: Increase the tank size for the Reddington ID product variant, ensuring no change to Marconi-HI ADF.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Supports higher ink capacity and longer use between refills.</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Tank size increased as per specifications; no interference with ADF operation.</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Tank size increased as per specifications; no interference with ADF operation.</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>Supports higher ink capacity and longer use between refills.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>8</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>R&amp;D</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Performance/Feature</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>HW Spec</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Input and Output Tray Redesign for Tank Protrusion: Modify input and output trays to accommodate the increased tank protrusion due to larger ink tanks.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Ensures mechanical compatibility and user convenience.</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Trays function correctly with new tank dimensions; verified in assembly and user testing.</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Trays function correctly with new tank dimensions.</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>Ensures mechanical compatibility and user convenience.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>9</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Design/UI</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Control Panel</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>4.3” CGD Display Integration: Integrate a 4.3” CGD display into the product for improved user interface.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Enhances usability and aligns with modern user expectations.</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Display operates with full functionality; passes usability and reliability tests.</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Display operates with full functionality.</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>Enhances usability and aligns with modern user expectations.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>10</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>R&amp;D</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Quality Improvement &amp; Serviceability</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Print Quality</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Service Station Aerosol Management with Spit Platform Changes: Implement aerosol management in the service station to handle changes due to increased tank size and spit platform updates.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Maintains print quality and prevents contamination inside the printer.</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>No aerosol-related print defects or contamination after 80,000 pages of operation.</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>No aerosol-related print defects or contamination after 80,000 pages of operation.</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>Maintains print quality and prevents contamination inside the printer.</t>
         </is>
       </c>
     </row>
@@ -876,7 +1408,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N2"/>
+  <dimension ref="A1:N4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1021,6 +1553,142 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>5</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Reliability</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Durability</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Warranty Page Life Goal of 80,000 Pages: Set and support a new warranty page life goal of 80,000 pages for the printer.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Enhances product value and aligns with new competitive benchmarks.</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Device must operate without major failure for 80,000 pages under standard usage conditions.</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Device operates without major failure for 80,000 pages under standard usage conditions.</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>extended supporting document</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>Enhances product value and aligns with new competitive benchmarks.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>7</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Rahul1</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Tech Reg</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Environmental &amp; Sustainability</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Environmental Ecolabel</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>PDL SKU</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>EPEAT3, LOT4, and Blue Angel Compliance for PDL SKU: Ensure the PDL SKU meets EPEAT3, LOT4, and Blue Angel environmental requirements.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Mandatory for market access and sustainability goals.</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Product passes all required certifications prior to launch.</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Product passes all required certifications prior to launch.</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>extended supporting document</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>Mandatory for market access and sustainability goals.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
